--- a/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le rejoindre. Rejoindre, c'est aller vers lui. Nora marche vers Adam. Elle dit : tu veux jouer ? Inviter, c'est demander. Adam hésite. Nora attend. Adam dit : d'accord. Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte. Nora dit : ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte. Papa dit : tu as repris le geste. Rejoindre. Inviter. Un adulte si ça continue. Nora et Inès se disent à demain.</t>
+          <t>Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le rejoindre. Rejoindre, c'est aller vers lui. Nora marche vers Adam. Tu veux jouer ? Inviter, c'est demander. Adam hésite. Nora attend. D'accord. Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte. Ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte si ça continue. Nora et Inès se disent à demain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le rejoindre. Rejoindre, c'est aller vers lui. Nora marche vers Adam.
+narrateur|Tu veux jouer ? Inviter, c'est demander.
+narrateur|Adam hésite. Nora attend.
+copain|D'accord.
+narrateur|Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte.
+enfant-f|Ça continue. On prévient un adulte si ça continue.
+narrateur|La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte.
+papa|Tu as repris le geste. Rejoindre. Inviter.
+narrateur|Un adulte si ça continue. Nora et Inès se disent à demain.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est à l'écart. Que fait Nora ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a su rejoindre. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora range son tablier. Papa l'attend près du portail.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Un adulte si ça continue. Nora et Inès se disent à demain.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Adam est à l'écart. Que fait Nora ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Nora a su rejoindre. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Deux fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Nora range son tablier. Papa l'attend près du portail.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nora rejoint Adam, puis Inès</t>
+          <t>Sarah rejoint Aniss près du muret</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.MOQ.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, une flaque brille près du portail. Sarah voit Aniss près du muret. Elle le rejoint, l'invite aux plots, prévient la maîtresse. À l'atelier, elle reprend le geste. Papa l'écoute à la sortie.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le rejoindre. Rejoindre, c'est aller vers lui. Nora marche vers Adam. Tu veux jouer ? Inviter, c'est demander. Adam hésite. Nora attend. D'accord. Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte. Ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte si ça continue. Nora et Inès se disent à demain.</t>
+          <t>Près du portail de l'école, une flaque ronde brille. Le ciel s'y cache, tout petit. Un manteau bleu goutte encore. Goutte, goutte, sur les dalles froides. L'herbe coupée sent fort, après la pluie. Les crochets du portail sont lisses et froids. Ton manteau est lourd, Sarah. On le secoue un peu ? Oui, papa. Ils secouent le manteau bleu. Des gouttes partent, toutes petites. Ça sent le tissu mouillé. Tu vas jouer, là-bas ? Je reviens te chercher, à la sortie. Oui. En ce moment, Sarah est dans la cour. Le sol est encore sombre, un peu mou. Des plots jaunes brillent, plus loin. Un oiseau secoue ses plumes, sur le muret. Aniss est à l'écart. Il est près du muret. Ses épaules sont basses. Il tient un plot, sans bouger. Sarah le voit. Aniss est tout seul. Sarah se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Sarah marche vers Aniss. Ses chaussures font un petit bruit mou. Tu veux jouer ? Inviter, c'est demander. Aniss hésite. Sarah attend, tout près. Le plot est lisse, dans sa main. Aniss dit d'accord, tout bas. Ils marchent vers les plots jaunes. Les plots sentent le plastique tiède. Ils les alignent, un, puis deux. Ça continue un peu, plus loin. Sarah va vers la maîtresse. La maîtresse est l'adulte, dans la cour. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Sarah. Je reste près de vous. La maîtresse s'approche. Elle reste près d'eux. Aniss pose un plot. Sarah en pose un autre. Bravo, Sarah. Tu as rejoint Aniss. Tu l'as invité. Tu as prévenu un adulte. On joue ensemble, maintenant. Oui. Les plots sont bien alignés. Plus tard, c'est l'atelier peinture. Ça sent les pots et l'eau. Un tablier bleu attend sur le crochet. Un pinceau goutte dans un verre. Aniss est à l'écart, près des pots. Sarah se souvient encore. Elle va rejoindre Aniss. Tu veux peindre avec moi ? Aniss dit oui, tout bas. Ils trempent le pinceau. L'eau devient un peu bleue. Le papier est rêche sous les doigts. Ça continue encore, un peu. Sarah prévient la maîtresse. Je suis là. On continue ensemble, près de moi. Bravo. Tu as repris le geste. Le soir, papa attend près du portail. La flaque est plus petite, maintenant. Te voilà, Sarah. Ton tablier a une tache bleue. J'ai rejoint Aniss. Je l'ai invité. Ça continuait. J'ai prévenu un adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte, si ça continue. Bravo. Tu as fait du bon travail. Tu as fini de ranger ton tablier ? Oui, papa. Sarah et Aniss se disent à demain. Le manteau bleu est presque sec.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1329,106 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le rejoindre. Rejoindre, c'est aller vers lui. Nora marche vers Adam.
-narrateur|Tu veux jouer ? Inviter, c'est demander.
-narrateur|Adam hésite. Nora attend.
-copain|D'accord.
-narrateur|Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte.
-enfant-f|Ça continue. On prévient un adulte si ça continue.
-narrateur|La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte.
-papa|Tu as repris le geste. Rejoindre. Inviter.
-narrateur|Un adulte si ça continue. Nora et Inès se disent à demain.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Près du portail de l'école, une flaque ronde brille.
+narrateur|Le ciel s'y cache, tout petit.
+narrateur|Un manteau bleu goutte encore.
+narrateur|Goutte, goutte, sur les dalles froides.
+narrateur|L'herbe coupée sent fort, après la pluie.
+narrateur|Les crochets du portail sont lisses et froids.
+papa|Ton manteau est lourd, Sarah.
+papa|On le secoue un peu ?
+enfant-f|Oui, papa.
+narrateur|Ils secouent le manteau bleu.
+narrateur|Des gouttes partent, toutes petites.
+narrateur|Ça sent le tissu mouillé.
+papa|Tu vas jouer, là-bas ?
+papa|Je reviens te chercher, à la sortie.
+enfant-f|Oui.
+narrateur|En ce moment, Sarah est dans la cour.
+narrateur|Le sol est encore sombre, un peu mou.
+narrateur|Des plots jaunes brillent, plus loin.
+narrateur|Un oiseau secoue ses plumes, sur le muret.
+narrateur|Aniss est à l'écart.
+narrateur|Il est près du muret.
+narrateur|Ses épaules sont basses.
+narrateur|Il tient un plot, sans bouger.
+narrateur|Sarah le voit.
+enfant-f|Aniss est tout seul.
+narrateur|Sarah se souvient.
+narrateur|On peut rejoindre.
+narrateur|Rejoindre, c'est aller vers lui.
+narrateur|Sarah marche vers Aniss.
+narrateur|Ses chaussures font un petit bruit mou.
+enfant-f|Tu veux jouer ?
+narrateur|Inviter, c'est demander.
+narrateur|Aniss hésite.
+narrateur|Sarah attend, tout près.
+narrateur|Le plot est lisse, dans sa main.
+narrateur|Aniss dit d'accord, tout bas.
+narrateur|Ils marchent vers les plots jaunes.
+narrateur|Les plots sentent le plastique tiède.
+narrateur|Ils les alignent, un, puis deux.
+narrateur|Ça continue un peu, plus loin.
+narrateur|Sarah va vers la maîtresse.
+narrateur|La maîtresse est l'adulte, dans la cour.
+enfant-f|Ça continue.
+enfant-f|On prévient un adulte, si ça continue.
+maitresse|Je t'écoute, Sarah.
+maitresse|Je reste près de vous.
+narrateur|La maîtresse s'approche.
+narrateur|Elle reste près d'eux.
+narrateur|Aniss pose un plot.
+narrateur|Sarah en pose un autre.
+maitresse|Bravo, Sarah.
+maitresse|Tu as rejoint Aniss.
+maitresse|Tu l'as invité.
+maitresse|Tu as prévenu un adulte.
+enfant-f|On joue ensemble, maintenant.
+maitresse|Oui.
+maitresse|Les plots sont bien alignés.
+narrateur|Plus tard, c'est l'atelier peinture.
+narrateur|Ça sent les pots et l'eau.
+narrateur|Un tablier bleu attend sur le crochet.
+narrateur|Un pinceau goutte dans un verre.
+narrateur|Aniss est à l'écart, près des pots.
+narrateur|Sarah se souvient encore.
+narrateur|Elle va rejoindre Aniss.
+enfant-f|Tu veux peindre avec moi ?
+narrateur|Aniss dit oui, tout bas.
+narrateur|Ils trempent le pinceau.
+narrateur|L'eau devient un peu bleue.
+narrateur|Le papier est rêche sous les doigts.
+narrateur|Ça continue encore, un peu.
+narrateur|Sarah prévient la maîtresse.
+maitresse|Je suis là.
+maitresse|On continue ensemble, près de moi.
+maitresse|Bravo.
+maitresse|Tu as repris le geste.
+narrateur|Le soir, papa attend près du portail.
+narrateur|La flaque est plus petite, maintenant.
+papa|Te voilà, Sarah.
+papa|Ton tablier a une tache bleue.
+enfant-f|J'ai rejoint Aniss.
+enfant-f|Je l'ai invité.
+enfant-f|Ça continuait.
+enfant-f|J'ai prévenu un adulte.
+papa|Tu as repris le geste.
+papa|Rejoindre.
+papa|Inviter.
+papa|Un adulte, si ça continue.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Tu as fini de ranger ton tablier ?
+enfant-f|Oui, papa.
+narrateur|Sarah et Aniss se disent à demain.
+narrateur|Le manteau bleu est presque sec.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1453,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam est à l'écart. Que fait Nora ?</t>
+          <t>Aniss est à l'écart. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1609,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam est à l'écart. Que fait Nora ?</t>
+          <t>narrateur|Aniss est à l'écart.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1638,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora a su rejoindre. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Deux fois.</t>
+          <t>Sarah a su rejoindre Aniss. Elle a pu l'inviter. Elle a prévenu un adulte, car ça continue. Deux fois, tu as repris le geste. Bravo, Sarah. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1782,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora a su rejoindre. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Deux fois.</t>
+          <t>narrateur|Sarah a su rejoindre Aniss.
+narrateur|Elle a pu l'inviter.
+narrateur|Elle a prévenu un adulte, car ça continue.
+papa|Deux fois, tu as repris le geste.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|J'ai rejoint.
+enfant-f|J'ai invité.
+papa|Oui.
+papa|Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1819,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nora range son tablier. Papa l'attend près du portail.</t>
+          <t>Sarah range son tablier, près du portail. On rentre, maintenant ? Oui, papa. Tu as les mains un peu bleues. C'est la peinture. On les lave, à la maison. Aniss t'a dit à demain ? Oui. La flaque ne brille plus. Le manteau bleu sent encore la cour.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1955,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nora range son tablier. Papa l'attend près du portail.</t>
+          <t>narrateur|Sarah range son tablier, près du portail.
+papa|On rentre, maintenant ?
+enfant-f|Oui, papa.
+papa|Tu as les mains un peu bleues.
+enfant-f|C'est la peinture.
+papa|On les lave, à la maison.
+papa|Aniss t'a dit à demain ?
+enfant-f|Oui.
+narrateur|La flaque ne brille plus.
+narrateur|Le manteau bleu sent encore la cour.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1992,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai rejoint Aniss. Je l'ai invité. Bravo. Tu as fait du bon travail. Le portail cliquette, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2132,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai rejoint Aniss.
+enfant-f|Je l'ai invité.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le portail cliquette, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2197,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Près du portail de l'école, une flaque ronde brille. Le ciel s'y cache, tout petit. Un manteau bleu goutte encore. Goutte, goutte, sur les dalles froides. L'herbe coupée sent fort, après la pluie. Les crochets du portail sont lisses et froids. Ton manteau est lourd, Sarah. On le secoue un peu ? Oui, papa. Ils secouent le manteau bleu. Des gouttes partent, toutes petites. Ça sent le tissu mouillé. Tu vas jouer, là-bas ? Je reviens te chercher, à la sortie. Oui. En ce moment, Sarah est dans la cour. Le sol est encore sombre, un peu mou. Des plots jaunes brillent, plus loin. Un oiseau secoue ses plumes, sur le muret. Aniss est à l'écart. Il est près du muret. Ses épaules sont basses. Il tient un plot, sans bouger. Sarah le voit. Aniss est tout seul. Sarah se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Sarah marche vers Aniss. Ses chaussures font un petit bruit mou. Tu veux jouer ? Inviter, c'est demander. Aniss hésite. Sarah attend, tout près. Le plot est lisse, dans sa main. Aniss dit d'accord, tout bas. Ils marchent vers les plots jaunes. Les plots sentent le plastique tiède. Ils les alignent, un, puis deux. Ça continue un peu, plus loin. Sarah va vers la maîtresse. La maîtresse est l'adulte, dans la cour. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Sarah. Je reste près de vous. La maîtresse s'approche. Elle reste près d'eux. Aniss pose un plot. Sarah en pose un autre. Bravo, Sarah. Tu as rejoint Aniss. Tu l'as invité. Tu as prévenu un adulte. On joue ensemble, maintenant. Oui. Les plots sont bien alignés. Plus tard, c'est l'atelier peinture. Ça sent les pots et l'eau. Un tablier bleu attend sur le crochet. Un pinceau goutte dans un verre. Aniss est à l'écart, près des pots. Sarah se souvient encore. Elle va rejoindre Aniss. Tu veux peindre avec moi ? Aniss dit oui, tout bas. Ils trempent le pinceau. L'eau devient un peu bleue. Le papier est rêche sous les doigts. Ça continue encore, un peu. Sarah prévient la maîtresse. Je suis là. On continue ensemble, près de moi. Bravo. Tu as repris le geste. Le soir, papa attend près du portail. La flaque est plus petite, maintenant. Te voilà, Sarah. Ton tablier a une tache bleue. J'ai rejoint Aniss. Je l'ai invité. Ça continuait. J'ai prévenu un adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte, si ça continue. Bravo. Tu as fait du bon travail. Tu as fini de ranger ton tablier ? Oui, papa. Sarah et Aniss se disent à demain. Le manteau bleu est presque sec.</t>
+          <t>Près du portail de l'école, une flaque ronde brille. Le ciel s'y cache, tout petit. Un manteau bleu goutte encore. Goutte, goutte, sur les dalles froides. L'herbe coupée sent fort, après la pluie. Les crochets du portail sont lisses et froids. Ton manteau est lourd, Sarah. On le secoue un peu ? Oui, papa. Ils secouent le manteau bleu. Des gouttes partent, toutes petites. Ça sent le tissu mouillé. Tu vas jouer, là-bas ? Je reviens te chercher, à la sortie. Oui. En ce moment, Sarah est dans la cour. Le sol est encore sombre, un peu mou. Des plots jaunes brillent, plus loin. Un oiseau secoue ses plumes, sur le muret. Aniss est à l'écart. Il est près du muret. Ses épaules sont basses. Il tient un plot, sans bouger. Sarah le voit. Aniss est tout seul. Sarah se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Sarah marche vers Aniss. Ses chaussures font un petit bruit mou. Tu veux jouer ? Inviter, c'est demander. Aniss hésite. Sarah attend, tout près. Le plot est lisse, dans sa main. Aniss dit d'accord, tout bas. Ils marchent vers les plots jaunes. Les plots sentent le plastique tiède. Ils les alignent, un, puis deux. Ça continue un peu, plus loin. Sarah va vers la maîtresse. La maîtresse est l'adulte, dans la cour. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Sarah. Je reste près de vous. La maîtresse s'approche. Elle reste près d'eux. Aniss pose un plot. Sarah en pose un autre. Bravo, Sarah. Tu as rejoint Aniss. Tu l'as invité. Tu as prévenu un adulte. On joue ensemble, maintenant. Oui. Les plots sont bien alignés. Plus tard, c'est l'atelier peinture. Ça sent les pots et l'eau. Un tablier bleu attend sur le crochet. Un pinceau goutte dans un verre. Aniss est à l'écart, près des pots. Sarah se souvient encore. Elle va rejoindre Aniss. Tu veux peindre avec moi ? Aniss dit oui, tout bas. Ils trempent le pinceau. L'eau devient un peu bleue. Le papier est rêche sous les doigts. Ça continue encore, un peu. Sarah prévient la maîtresse. Je suis là. On continue ensemble, près de moi. Bravo. Tu as repris le geste. Le soir, papa attend près du portail. La flaque est plus petite, maintenant. Te voilà, Sarah. Ton tablier a une tache bleue. J'ai rejoint Aniss. Je l'ai invité. Ça continuait. J'ai prévenu un adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte, si ça continue. Bravo. Tu as fini de ranger ton tablier ? Oui, papa. Sarah et Aniss se disent à demain. Le manteau bleu est presque sec.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora est à l'école. Papa l'a déposée. La récréation sent l'herbe. Adam est à l'écart. Il est près du muret. Ses épaules sont basses. Nora se souvient. Elle peut le &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt;. Rejoindre, c'est aller vers lui. Nora marche vers Adam. Elle dit : tu veux jouer ? Inviter, c'est demander. Adam hésite. Nora attend. Adam dit : d'accord. Ils marchent vers les plots. Un enfant les écarte encore. Ça continue un peu. Nora va vers la maîtresse. La maîtresse est l'adulte. Nora dit : ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Plus tard, c'est l'atelier peinture. Inès est à l'écart près des pots. Nora se souvient. Elle va rejoindre Inès. Elle l'invite. Inès dit oui. Un camarade les écarte encore. Ça continue. Nora prévient papa, à la sortie. Papa est l'adulte. Papa dit : tu as repris le geste. Rejoindre. Inviter. Un adulte si ça continue. Nora et Inès se disent à demain.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Près du portail de l'école, une flaque ronde brille. Le ciel s'y cache, tout petit. Un manteau bleu goutte encore. Goutte, goutte, sur les dalles froides. L'herbe coupée sent fort, après la pluie. Les crochets du portail sont lisses et froids. Ton manteau est lourd, Sarah. On le secoue un peu ? Oui, papa. Ils secouent le manteau bleu. Des gouttes partent, toutes petites. Ça sent le tissu mouillé. Tu vas jouer, là-bas ? Je reviens te chercher, à la sortie. Oui. En ce moment, Sarah est dans la cour. Le sol est encore sombre, un peu mou. Des plots jaunes brillent, plus loin. Un oiseau secoue ses plumes, sur le muret. Aniss est à l'écart. Il est près du muret. Ses épaules sont basses. Il tient un plot, sans bouger. Sarah le voit. Aniss est tout seul. Sarah se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Sarah marche vers Aniss. Ses chaussures font un petit bruit mou. Tu veux jouer ? Inviter, c'est demander. Aniss hésite. Sarah attend, tout près. Le plot est lisse, dans sa main. Aniss dit d'accord, tout bas. Ils marchent vers les plots jaunes. Les plots sentent le plastique tiède. Ils les alignent, un, puis deux. Ça continue un peu, plus loin. Sarah va vers la maîtresse. La maîtresse est l'adulte, dans la cour. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Sarah. Je reste près de vous. La maîtresse s'approche. Elle reste près d'eux. Aniss pose un plot. Sarah en pose un autre. Bravo, Sarah. Tu as rejoint Aniss. Tu l'as invité. Tu as prévenu un adulte. On joue ensemble, maintenant. Oui. Les plots sont bien alignés. Plus tard, c'est l'atelier peinture. Ça sent les pots et l'eau. Un tablier bleu attend sur le crochet. Un pinceau goutte dans un verre. Aniss est à l'écart, près des pots. Sarah se souvient encore. Elle va rejoindre Aniss. Tu veux peindre avec moi ? Aniss dit oui, tout bas. Ils trempent le pinceau. L'eau devient un peu bleue. Le papier est rêche sous les doigts. Ça continue encore, un peu. Sarah prévient la maîtresse. Je suis là. On continue ensemble, près de moi. Bravo. Tu as repris le geste. Le soir, papa attend près du portail. La flaque est plus petite, maintenant. Te voilà, Sarah. Ton tablier a une tache bleue. J'ai rejoint Aniss. Je l'ai invité. Ça continuait. J'ai prévenu un adulte. Tu as repris le geste. Rejoindre. Inviter. Un adulte, si ça continue. Bravo. Tu as fini de ranger ton tablier ? Oui, papa. Sarah et Aniss se disent à demain. Le manteau bleu est presque sec.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1417,7 +1417,6 @@
 papa|Inviter.
 papa|Un adulte, si ça continue.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|Tu as fini de ranger ton tablier ?
 enfant-f|Oui, papa.
 narrateur|Sarah et Aniss se disent à demain.
@@ -1458,7 +1457,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam est à l'écart. Que fait Nora ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est à l'écart. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1613,7 +1612,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1638,12 +1636,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a su rejoindre Aniss. Elle a pu l'inviter. Elle a prévenu un adulte, car ça continue. Deux fois, tu as repris le geste. Bravo, Sarah. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
+          <t>Sarah a su rejoindre Aniss. Elle a pu l'inviter. Elle a prévenu un adulte, car ça continue. Deux fois, tu as repris le geste. Bravo, Sarah. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora a su &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt;. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Deux fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a su rejoindre Aniss. Elle a pu l'inviter. Elle a prévenu un adulte, car ça continue. Deux fois, tu as repris le geste. Bravo, Sarah. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1787,14 +1785,12 @@
 narrateur|Elle a prévenu un adulte, car ça continue.
 papa|Deux fois, tu as repris le geste.
 papa|Bravo, Sarah.
-papa|C'est du bon travail.
 enfant-f|J'ai rejoint.
 enfant-f|J'ai invité.
 papa|Oui.
 papa|Et un adulte, si ça continue.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1824,7 +1820,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora range son tablier. Papa l'attend près du portail.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range son tablier, près du portail. On rentre, maintenant ? Oui, papa. Tu as les mains un peu bleues. C'est la peinture. On les lave, à la maison. Aniss t'a dit à demain ? Oui. La flaque ne brille plus. Le manteau bleu sent encore la cour.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1967,7 +1963,6 @@
 narrateur|Le manteau bleu sent encore la cour.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1992,12 +1987,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai rejoint Aniss. Je l'ai invité. Bravo. Tu as fait du bon travail. Le portail cliquette, tout doux. L'histoire est finie.</t>
+          <t>J'ai rejoint Aniss. Je l'ai invité. Bravo. Le portail cliquette, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai rejoint Aniss. Je l'ai invité. Bravo. Le portail cliquette, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2135,12 +2130,9 @@
           <t>enfant-f|J'ai rejoint Aniss.
 enfant-f|Je l'ai invité.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le portail cliquette, tout doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le portail cliquette, tout doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2159,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2204,6 +2196,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-02.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis atelier</t>
+          <t>école, récréation puis atelier peinture</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nora, Adam, Inès, papa</t>
+          <t>Sarah, Aniss, papa, maîtresse</t>
         </is>
       </c>
     </row>
